--- a/analysis/CASE_D1/OUTWARD_FACING_PACKAGE/CASE_D1_participant_workbook.xlsx
+++ b/analysis/CASE_D1/OUTWARD_FACING_PACKAGE/CASE_D1_participant_workbook.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Participant_Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Participant Summary" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,27 +25,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002980B9"/>
-        <bgColor rgb="002980B9"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,24 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -436,1414 +413,1592 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Anonymized Code</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Speaker Type</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Segments</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Chars</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Questions</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Top Codes</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>anonymized_code</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>source_file</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>table_id</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>speaker_type</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>segment_count</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>total_chars</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>questions_covered</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>top_codes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>D1_M01</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>HWCH0AR.docx</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>moderator</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>140</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>17289</v>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>17289</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>Q1;Q2;Q3;Q5</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>general_response;practical_recommendation;healthcare_system_critique;pillar_social;interdependent_care</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>D1_M02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>HWCH2AR.docx</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>moderator</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>D1_M03</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>HWCH3AR.docx</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>moderator</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>20413</v>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>20413</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>general_response;healthcare_worker_wellbeing;awareness_education;healthcare_system_critique;training_deficit</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>D1_M04</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>HWCH4AR.docx</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>moderator</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>15191</v>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>15191</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>Q1;Q2;Q3;Q4;Q5;Q6;Q7</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>general_response;professional_identity</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>D1_M05</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>HWCH6AR.docx</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>moderator</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>766</v>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>766</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>general_response</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>D1_M06</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>HWCH7AR.docx</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>moderator</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>6110</v>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>6110</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>Q1;Q2;Q3;Q4;Q5;Q6;Q7</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>general_response</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>D1_M07</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>HWCH10AR.docx</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>moderator</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>380</v>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>Q2;Q3</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>contentment_as_core;safety_security;spiritual_moral_anchor</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>D1_M08</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>HWCH10AR.docx</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>moderator</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>384</v>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>384</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>healthcare_system_critique;hidden_masked_distress;practical_recommendation;professional_identity;service_recipient_voice</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>D1_P01</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>HWCH0AR.docx</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>participant</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>15833</v>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>15833</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>Q1;Q2;Q3;Q5</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>general_response;practical_recommendation;school_clinical_link;spiritual_moral_anchor;family_support_ecology</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>D1_P02</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>HWCH0AR.docx</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>participant</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>192</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>19700</v>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>19700</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>Q1;Q2;Q3;Q5</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>general_response;school_clinical_link;practical_recommendation;awareness_education;service_recipient_voice</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>D1_P03</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>HWCH0AR.docx</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>participant</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>102</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>13163</v>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>13163</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>Q1;Q2;Q3;Q5</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>general_response;spiritual_moral_anchor;awareness_education;healthcare_system_critique;pillar_physical</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>D1_P04</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>HWCH0AR.docx</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>participant</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>6280</v>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>6280</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>general_response;family_support_ecology;practical_recommendation;child_vulnerability;training_deficit</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>D1_P05</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>HWCH0AR.docx</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>participant</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>2032</v>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2032</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>Q1;Q2;Q3</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>general_response;practical_recommendation;spiritual_moral_anchor;balance_multidimensional</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>D1_P06</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>HWCH2AR.docx</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>participant</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>10255</v>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>10255</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>Q6</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>general_response;healthcare_system_critique;family_support_ecology</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>D1_P07</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>HWCH2AR.docx</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>participant</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>18975</v>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>18975</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>general_response;healthcare_system_critique;family_support_ecology</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>D1_P08</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>HWCH4AR.docx</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>participant</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>985</v>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>general_response</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>D1_P09</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>HWCH4AR.docx</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>participant</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>923</v>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>Q3;Q6;Q7</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>general_response</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>D1_P10</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>HWCH6AR.docx</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>participant</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>26630</v>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>26630</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>Q1;Q2;Q3;Q4;Q5;Q6</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>general_response;cultural_local_adaptation;healthcare_system_critique;pillar_emotional;interdependent_care</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>D1_P11</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>HWCH6AR.docx</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>participant</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>9126</v>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>9126</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>Q3;Q5</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>general_response;balance_multidimensional</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>D1_P12</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>HWCH6AR.docx</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>participant</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>2629</v>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2629</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>awareness_education;interdependent_care;early_detection_prevention;general_response</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>D1_P13</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>HWCH6AR.docx</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>participant</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>265</v>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>general_response</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>D1_P14</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>HWCH6AR.docx</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>participant</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>239</v>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>general_response</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>D1_P15</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>HWCH7AR.docx</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>participant</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>12656</v>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>12656</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>Q1;Q2;Q3;Q4;Q5;Q6;Q7</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>general_response</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>D1_P16</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>HWCH7AR.docx</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>participant</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>9365</v>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>9365</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
         <is>
           <t>Q1;Q2;Q3;Q4;Q5;Q6;Q7</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>general_response</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>D1_P17</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>HWCH7AR.docx</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>participant</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>6223</v>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
         <is>
           <t>Q1;Q2;Q3;Q4;Q5;Q7</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>general_response</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>D1_P18</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>HWCH7AR.docx</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>participant</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>3595</v>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>3595</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
         <is>
           <t>Q1;Q3;Q4;Q5;Q6;Q7</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>general_response</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>D1_P19</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>HWCH7AR.docx</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>participant</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>3259</v>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>3259</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
         <is>
           <t>Q1;Q3;Q6;Q7</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>general_response</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>D1_P20</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>HWCH7AR.docx</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>participant</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>2554</v>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2554</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
         <is>
           <t>Q5;Q6;Q7</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>general_response</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>D1_P21</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>HWCH7AR.docx</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>participant</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>2475</v>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2475</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
         <is>
           <t>Q3;Q5</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>general_response</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>D1_P22</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>HWCH10AR.docx</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>participant</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>811</v>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>811</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
         <is>
           <t>Q1;Q2;Q3;Q4</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>pillar_emotional;pillar_physical;cultural_local_adaptation;general_response;pillar_social</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>D1_P23</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>HWCH10AR.docx</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>participant</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="F31" s="2" t="n">
-        <v>1368</v>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1368</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
         <is>
           <t>Q1;Q2;Q3;Q4</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>pillar_emotional;cultural_local_adaptation;pillar_social;pillar_intellectual;medical_model_dominance</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>D1_P24</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>HWCH10AR.docx</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>participant</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>1060</v>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1060</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
         <is>
           <t>Q2;Q3;Q4</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>pillar_physical;pillar_intellectual;healthcare_system_critique;awareness_education;professional_identity</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>D1_P25</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>HWCH10AR.docx</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>participant</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>1005</v>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
         <is>
           <t>Q1;Q3;Q4</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>balance_multidimensional;pillar_physical;spiritual_moral_anchor;cultural_local_adaptation;healthcare_worker_wellbeing</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>D1_P26</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>HWCH10AR.docx</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>participant</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>966</v>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>966</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
         <is>
           <t>Q1;Q2;Q3;Q4</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>general_response;pillar_social;child_rights_inclusion;child_vulnerability;family_support_ecology</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>D1_P27</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>HWCH10AR.docx</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>participant</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F35" s="2" t="n">
-        <v>949</v>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
         <is>
           <t>Q3;Q4</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>interdependent_care;training_deficit;child_vulnerability;school_clinical_link;balance_multidimensional</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>D1_U01</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>HWCH0AR.docx</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>unclear</t>
         </is>
       </c>
-      <c r="E36" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>166</v>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
         <is>
           <t>Q3;Q5</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>general_response</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>D1_U02</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>HWCH6AR.docx</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>unclear</t>
         </is>
       </c>
-      <c r="E37" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F37" s="2" t="n">
-        <v>978</v>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>978</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
         <is>
           <t>Q6</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>general_response</t>
         </is>
